--- a/www/download/COUNTRY.WAF.EXI382.xlsx
+++ b/www/download/COUNTRY.WAF.EXI382.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -498,6 +498,11 @@
           <t>Country</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Resto do mundo - Africa</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -505,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -962,2643 +972,4879 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.17499754601227</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.17499754601227</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.17499754601227</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.17499754601227</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.17499754601227</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.17524601226994</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.17524601226994</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.17524601226994</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.17524601226994</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.17524601226994</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.17524601226994</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.17524601226994</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.17524601226994</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.17524601226994</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.17524601226994</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.17524601226994</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.17524601226994</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.17524601226994</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.17524601226994</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.17524601226994</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.17524601226994</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.17524601226994</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.17524601226994</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.17524601226994</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.17524601226994</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.17524601226994</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.17524601226994</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>509.606</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>226.434</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>232.371</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>238.824</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>245.646</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>252.473</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>259.664</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>268.625</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>276.5</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>284.3</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>292.033</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>299.341</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>306.807</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>322.316</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>328.615</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>335.848</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>349.548</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>359.598</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>368.903</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>385.541</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>392.786</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>423.836</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>406.319</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>409.76</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>412.145</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>452.678</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>464.149</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>421.049</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>151.57</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>193.136</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>199.224</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>178.221</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>209.804</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>215.542</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>221.794</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>228.11</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>234.322</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>240.183</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>245.13</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>251.235</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>264.129</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>268.167</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>273.668</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>282.859</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>293.758</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>304.271</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>322.021</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>326.709</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>353.593</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>338.213</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>342.196</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>343.657</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>376.266</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>385.211</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>1152128.951</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>513668</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>527164</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>541782</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>557220</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>572673</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>588924</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>608937</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>626418</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>643870</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>661153</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>677546</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>694189</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>728739</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>742967</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>759096</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>789675</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>812305</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>833344</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>872184.635</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>887118.65</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>959002.733</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>918913.862</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>927625.88</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>932634.105</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>1023921.84</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>1049544.496</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>959758.346</t>
+          <t>1566238051229.28</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>349468</t>
+          <t>821380972685.256</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>358616</t>
+          <t>839268220991.6</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>368084</t>
+          <t>891181976290.274</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>376466</t>
+          <t>911759996421.256</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>385659</t>
+          <t>941680797850.345</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>395592</t>
+          <t>958371940619.132</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>404007</t>
+          <t>964888672039.162</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>414776</t>
+          <t>994959420948.995</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>425362</t>
+          <t>1021364323604.48</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>434551</t>
+          <t>1042620425002.8</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>440838</t>
+          <t>1070464945528.8</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>451575</t>
+          <t>1089330329973.09</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>474799</t>
+          <t>1165519350363.93</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>479309</t>
+          <t>1151833977170.25</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>487994</t>
+          <t>1188218726344.34</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>499305</t>
+          <t>1276838564478.34</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>525179</t>
+          <t>1268505401918.89</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>553050</t>
+          <t>1271841223602.18</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>734280.063</t>
+          <t>1192718351637.57</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>744089.585</t>
+          <t>1185365992674.1</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>806729.156</t>
+          <t>1303602797956.62</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>771291.996</t>
+          <t>1215200249304.72</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>780974.335</t>
+          <t>1229490168573.38</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>783977.175</t>
+          <t>1275091140919.13</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>858089.37</t>
+          <t>1401376364775.38</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>878220.897</t>
+          <t>1436336071136.01</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>435735089679.225</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>189762824737.754</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>194369672958.922</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>219785804759.488</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>214745725956.367</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>240791861979.444</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>250052860275.718</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>256161068750.927</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>264077583751.155</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>279435693431.082</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>289743586190.433</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>286013310892.06</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>235514949492.425</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>290453143629.047</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>294230225362.872</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>273630899986.54</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>321978686439.2</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>284421980758.112</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>292398307464.731</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>351176064554.353</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>357639981506.45</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>396988491842.533</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>330753633744.244</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>369815622111.776</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>370973150250.939</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>402214935946.898</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>426177083620.865</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>12505512580898.2</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>197900823.340385</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>169994217.761405</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>170964556.434051</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>170128329.804036</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>154154343.586094</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>145988450.673565</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>139776968.501832</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>150083009.900591</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>145543307.947375</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>4540863578.33815</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>111565479.285598</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>104795084.998361</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>105121671.38702</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>108838651.726881</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>86649043.2064511</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>92197032.5082085</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>76179550.5166438</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>73665282.0689146</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>3091623799597.22</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>1218571684207.83</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>1489715456571.59</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>3018017729996.54</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>1604872562325.72</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>1553106375862.73</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>1694916477843.62</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>1774369953689.43</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>3533336.21426342</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>3323122.14677924</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>3697594.42449748</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>3950958.84057472</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>4222971.29068318</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>5267741.29089775</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5281710.88108188</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>5283067.9765816</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>5026771.72286111</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>4998581.27539024</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>5513538.22275203</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>6043301.56217104</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>6375978.42466799</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>6720279.93633029</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>6865803.10587427</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>8092963.84985542</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>8777425.57914397</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>9838174.11691194</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>9879436.38872863</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>10741227.3607367</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>12316448.6471808</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>12220224.8052394</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>12288995.4471975</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12205960.681708</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>13054396.7263584</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13633542.8483302</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>13693865.4089957</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>5838313.09703724</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>6241733.5037531</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>6946307.51611684</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>7583014.87512601</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>8183314.79712206</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>10103117.6279483</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10324302.7436554</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>10075981.8673741</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>9544428.37752898</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>9574699.96917848</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>10478097.3208938</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>11507829.9030191</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>12132865.5168169</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>13043920.9154542</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>12917989.7948842</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>15367660.2328327</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>17191751.2343225</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>18851701.6329939</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>18463292.6508413</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>17922070.8181264</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>20120576.7731025</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>20168609.5659476</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>19877140.6344853</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>19559288.6460513</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>21612630.0156621</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>22596432.9616712</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>22738148.2193936</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1.20261890396238</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>0.841604120738112</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0.845020339545043</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0.674739642092929</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0.753077963826776</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0.601628048513207</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0.582033493093511</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0.577160034387465</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0.570659630054374</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0.522217848325629</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>0.499777806002122</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0.541319872928903</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0.917394207769028</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>0.634683632849375</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>0.629027063446183</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>0.783402386294417</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0.550739291230207</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>0.846478245458578</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>0.891426817053643</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>1.09091717051595</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>1.08055481252163</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>1.03212227294907</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>1.33192297016933</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>1.11179379119806</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>1.11329896690809</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>1.13341000856226</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>1.06069479363515</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1034.87975190096</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1251.98142599271</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1006.38518022896</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1103.20947656614</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1204.94313509103</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>1147.69910001489</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1160.11199801273</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>1154.95039879764</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>1157.67648832215</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>1192.52862911344</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>1206.34510431814</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>1166.78216004621</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>937.428899208</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>1099.66396582342</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>1097.19027830781</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>999.864434228879</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>1138.30101371777</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>968.218672370609</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>960.979874732491</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>1090.53658627733</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>1094.67525237043</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>1122.72852072035</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>977.944840769211</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>1080.71391006945</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>1079.48649633834</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>1068.96509083221</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>1106.34596573996</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>-198882811378.157</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>-109813467481.101</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-101036928544.424</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>-99663891123.5066</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-105784536853.543</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>-123760515874.851</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.236</t>
+          <t>-111943065690.364</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.233</t>
+          <t>-100434770374.894</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>-107633573508.944</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.246</t>
+          <t>-109122354956.375</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.292</t>
+          <t>-116205326525.546</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.339</t>
+          <t>-117365911653.766</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.358</t>
+          <t>-131719811731.499</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>-126614247801.575</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.403</t>
+          <t>-120407771495.8</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.456</t>
+          <t>-140444937095.987</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.546</t>
+          <t>-127065133609.535</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>-170128831125.223</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.601</t>
+          <t>-162424689509.586</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>-156271209774.295</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0.731</t>
+          <t>-143060552880.997</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>0.698</t>
+          <t>-155264017830.139</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>0.685</t>
+          <t>-186683553087.214</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>0.724</t>
+          <t>-190157982892.285</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>0.787</t>
+          <t>-183476879066.291</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>0.815</t>
+          <t>-208009355905.789</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>-195022005515.143</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>-193457985877.897</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>-105560006589.904</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>-96820100810.34</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-95209445245.9351</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-101950701915.855</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-121707295494.832</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>-111545225873.028</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>-99780316839.7229</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>-104746404635.763</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>-107068688139.745</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>-113686994362.404</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>-115381930433.6</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>-127696947128.5</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>-124870891617.085</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>-118063993040.049</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>-137840105112.516</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>-126132035100.626</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>-170533583356.61</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>-160631542598.104</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>-154309363006.341</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>-140825161138.962</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>-151533775717.205</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>-186556692791.393</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>-189773901453.636</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>-182949868775.541</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>-207624473211.078</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>-194936631088.909</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>-5424825500.26012</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>-4253460891.19713</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>-4216827734.08375</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-4454445877.57153</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-3833834937.68766</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-2053220380.01963</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-397839817.335181</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>-654453535.170965</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>-2887168873.18158</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>-2053666816.6304</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>-2518332163.14286</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>-1983981220.16639</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>-4022864602.99842</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>-1743356184.48972</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>-2343778455.75052</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>-2604831983.47165</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>-933098508.908739</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>404752231.386905</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>-1793146911.48147</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>-1961846767.95387</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>-2235391742.03464</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>-3730242112.934</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>-126860295.8208</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>-384081438.648537</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>-527010290.749511</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>-384882694.711019</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>-85374426.2336163</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.505</t>
+          <t>2279.44570486495</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.533</t>
+          <t>2305.65415319575</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.613</t>
+          <t>1856.80112693914</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.621</t>
+          <t>1847.58864393791</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.658</t>
+          <t>2112.35925779244</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.775</t>
+          <t>1838.18706983721</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.824</t>
+          <t>1835.33603659577</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.836</t>
+          <t>1821.5416106835</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.812</t>
+          <t>1818.31572487072</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.881</t>
+          <t>1815.28836387576</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>1.041</t>
+          <t>1809.24961383567</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>1.254</t>
+          <t>1798.38453065814</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>1.345</t>
+          <t>1797.42074153672</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>1.548</t>
+          <t>1797.60268656578</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>1.469</t>
+          <t>1787.35265711347</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1.823</t>
+          <t>1783.1606179747</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1765.20810721932</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>2.251</t>
+          <t>1787.79471537912</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>2.272</t>
+          <t>1817.62310571788</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>2.414</t>
+          <t>2280.22167332313</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>2.497</t>
+          <t>2277.53186446764</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>2.446</t>
+          <t>2281.52163343099</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2.459</t>
+          <t>2280.49203774831</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>2.532</t>
+          <t>2282.24492534605</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2.836</t>
+          <t>2281.27769750304</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2.932</t>
+          <t>2280.5408235851</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>3.031</t>
+          <t>2279.84137155959</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>2260.82313674809</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>2268.51091267214</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>2268.63076717804</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>2268.54085016504</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>2268.38621430874</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>2268.25442720696</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.236</t>
+          <t>2268.02329163812</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.233</t>
+          <t>2266.86644951146</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>2265.52622061555</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.246</t>
+          <t>2264.7555399232</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.292</t>
+          <t>2263.96674348429</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.339</t>
+          <t>2263.45873101327</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.358</t>
+          <t>2262.62438601472</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>2260.94577991778</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.403</t>
+          <t>2260.90409750077</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.456</t>
+          <t>2260.23677377874</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.546</t>
+          <t>2259.1317930582</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>2258.92524430178</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.601</t>
+          <t>2258.97864750352</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>2262.23591584249</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>0.731</t>
+          <t>2258.53031524814</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>0.698</t>
+          <t>2262.6767224512</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>0.685</t>
+          <t>2261.55770161123</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>0.724</t>
+          <t>2263.82706567166</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>0.787</t>
+          <t>2262.87690285709</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.815</t>
+          <t>2261.91958038715</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>2261.22419907763</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>81716.2034141763</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>101301.762615095</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>116414.613268908</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>99567.9176764595</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>118577.705432687</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>179899.145977188</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>176990.520637004</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>169191.843919604</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>168454.330328004</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>188298.233269175</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>246393.771483906</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>320303.866965068</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>316171.781848139</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>390626.897906555</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>290391.299373924</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>406945.0306627</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>452094.438017052</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>554463.110719719</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>454651.010463996</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>431985.196103561</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>348514.011907096</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>316328.079126815</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>382554.476164102</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>432738.233061201</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>441597.082239796</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>474629.045127078</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>502238.333422361</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>204049508075.141</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>117782323360.475</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>111261419147.137</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>107849963815.814</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>120247503538.711</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>145967280035.92</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>136900246336.452</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>126055259202.178</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>129504190157.635</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>136511552172.179</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>150459618340.333</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>157072706076.853</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>160996664511.202</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>171578011895.002</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>157643995554.686</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>178492428875.044</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>170352025411.834</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>220074462328.285</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>203239893079.235</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>189828616594.91</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>165537852481.474</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>176100257214.728</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>217499015319.185</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>224787785175.702</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>215005237843.729</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>243819530709.19</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>231849707677.384</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>101263.629787746</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>113440.746791866</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>134030.365617977</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>134448.994760453</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>130466.865966081</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>145652.551527311</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>162383.580475802</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>174866.023278923</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>174449.579671818</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>182479.074365932</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>218600.841346804</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>258978.784037137</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>313255.784324972</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>366377.060344277</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>378438.612458594</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>457228.871430417</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>492170.504783078</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>547762.665783992</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>571614.582398822</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>570107.418965906</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>522031.534523312</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>515055.468853845</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>530173.806714283</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>591639.921213828</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>634969.391323209</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>659767.258192604</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>681361.669472713</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1152128.951</t>
+          <t>16240826656.1837</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>513668</t>
+          <t>10434745439.6624</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>527164</t>
+          <t>13521943071.4609</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>541782</t>
+          <t>14757609033.0875</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>557220</t>
+          <t>16643960576.2066</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>572673</t>
+          <t>16893727690.5365</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>588924</t>
+          <t>22601388110.9605</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>608937</t>
+          <t>26569969407.0602</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>626418</t>
+          <t>22889075560.9093</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>643870</t>
+          <t>26322022586.0039</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>661153</t>
+          <t>29605908009.4829</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>677546</t>
+          <t>30582131106.4908</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>694189</t>
+          <t>28914737197.1656</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>728739</t>
+          <t>41640582129.6934</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>742967</t>
+          <t>50196032217.1534</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>759096</t>
+          <t>44247590737.2858</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>789675</t>
+          <t>47908293711.1564</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>812305</t>
+          <t>49215073439.8207</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>833344</t>
+          <t>54213796751.7596</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>872184.635</t>
+          <t>48240640626.2646</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>887118.65</t>
+          <t>39250350692.4153</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>959002.733</t>
+          <t>41912577100.9824</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>918913.862</t>
+          <t>45034563140.4641</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>927625.88</t>
+          <t>50422994376.4241</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>932634.105</t>
+          <t>49176947838.5798</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>1023921.84</t>
+          <t>53776232571.6344</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>1049544.496</t>
+          <t>54280597662.9129</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>959758.346</t>
+          <t>-19547.4263735696</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>349468</t>
+          <t>-12138.9841767702</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>358616</t>
+          <t>-17615.7523490697</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>368084</t>
+          <t>-34881.0770839933</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>376466</t>
+          <t>-11889.1605333941</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>385659</t>
+          <t>34246.594449877</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>395592</t>
+          <t>14606.9401612022</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>404007</t>
+          <t>-5674.17935931891</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>414776</t>
+          <t>-5995.24934381399</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>425362</t>
+          <t>5819.15890324352</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>434551</t>
+          <t>27792.9301371021</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>440838</t>
+          <t>61325.0829279311</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>451575</t>
+          <t>2915.99752316664</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>474799</t>
+          <t>24249.8375622779</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>479309</t>
+          <t>-88047.31308467</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>487994</t>
+          <t>-50283.8407677177</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>499305</t>
+          <t>-40076.0667660259</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>525179</t>
+          <t>6700.44493572675</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>553050</t>
+          <t>-116963.571934825</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>734280.063</t>
+          <t>-138122.222862345</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>744089.585</t>
+          <t>-173517.522616216</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>806729.156</t>
+          <t>-198727.38972703</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>771291.996</t>
+          <t>-147619.330550181</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>780974.335</t>
+          <t>-158901.688152628</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>783977.175</t>
+          <t>-193372.309083413</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>858089.37</t>
+          <t>-185138.213065526</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>878220.897</t>
+          <t>-179123.336050352</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1301752.823</t>
+          <t>187808681418.957</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>669050.275</t>
+          <t>107347577920.812</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>682985.491</t>
+          <t>97739476075.6765</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>722279.143</t>
+          <t>93092354782.7267</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>738776.479</t>
+          <t>103603542962.504</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>763986.675</t>
+          <t>129073552345.384</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>775405.972</t>
+          <t>114298858225.492</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>783257.817</t>
+          <t>99485289795.1177</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>809914.369</t>
+          <t>106615114596.726</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>830461.225</t>
+          <t>110189529586.175</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>849370.643</t>
+          <t>120853710330.85</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>870032.33</t>
+          <t>126490574970.362</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>889988.317</t>
+          <t>132081927314.036</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>945488.237</t>
+          <t>129937429765.308</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>940091.065</t>
+          <t>107447963337.533</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>966211.574</t>
+          <t>134244838137.758</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>1032404.777</t>
+          <t>122443731700.678</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>1028223.58</t>
+          <t>170859388888.464</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>1037495.925</t>
+          <t>149026096327.475</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>989921.321</t>
+          <t>141587975968.645</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>986942.214</t>
+          <t>126287501789.059</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>1083330.059</t>
+          <t>134187680113.745</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>1011649.571</t>
+          <t>172464452178.721</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>1027140.155</t>
+          <t>174364790799.277</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>1060091.132</t>
+          <t>165828290005.149</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>1164840.451</t>
+          <t>190043298137.556</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>1193489.751</t>
+          <t>177569110014.471</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>4.22</t>
+          <t>156886.435651156</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>4.336</t>
+          <t>178641.068410847</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>4.846</t>
+          <t>203766.180442363</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>5.324</t>
+          <t>204061.009108753</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>5.751</t>
+          <t>226915.000324014</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>7.114</t>
+          <t>254427.854715095</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>7.257</t>
+          <t>270246.891096047</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>7.118</t>
+          <t>280475.50656018</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>6.777</t>
+          <t>272770.82446745</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>6.812</t>
+          <t>294658.103103242</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>7.448</t>
+          <t>355063.376767026</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>8.179</t>
+          <t>415224.602409662</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>8.635</t>
+          <t>440541.121412814</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>522481.952885866</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>9.204</t>
+          <t>474843.563232187</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>10.891</t>
+          <t>568763.499369327</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>12.129</t>
+          <t>647498.209923512</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>13.33</t>
+          <t>702910.452025125</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>13.076</t>
+          <t>749679.746799278</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>12.816</t>
+          <t>740838.105626868</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>14.268</t>
+          <t>795259.795484232</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>14.214</t>
+          <t>743856.404531362</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>13.925</t>
+          <t>759632.580906976</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13.74</t>
+          <t>795660.72791972</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>15.001</t>
+          <t>877364.651118668</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15.701</t>
+          <t>908571.531674566</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>15.787</t>
+          <t>943430.236172085</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>947884.352</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>437306.287</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>446751.528</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>464330.265</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>470510.592</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>490990.109</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>490284.296</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>505913.221</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>524016.074</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>533214.889</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>548623.227</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>562151.381</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>572457.238</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>600480.205</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>612190.087</t>
-        </is>
-      </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>625743.35</t>
-        </is>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>651903.074</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>661997.376</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>680543.536</t>
-        </is>
-      </c>
-      <c r="V33" t="inlineStr">
-        <is>
-          <t>714831.401</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>725600.441</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>789857.089</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>751294.696</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>767262.498</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>770176.772</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>845519.501</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>865021.753</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>3.073</t>
+          <t>148289.168540906</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2.834</t>
+          <t>169173.888903768</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>186906.672310552</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>3.423</t>
+          <t>197965.330951391</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>3.663</t>
+          <t>210865.374224377</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>4.572</t>
+          <t>259341.629800707</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>4.589</t>
+          <t>275976.775921047</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>4.598</t>
+          <t>271632.173939403</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>4.385</t>
+          <t>275184.291514859</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>4.374</t>
+          <t>287516.585127763</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>4.811</t>
+          <t>341781.648538343</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>5.285</t>
+          <t>395814.157786551</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>5.554</t>
+          <t>418800.336055507</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>5.906</t>
+          <t>502585.431919273</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>5.994</t>
+          <t>471613.240601077</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>7.053</t>
+          <t>533299.888110825</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>7.659</t>
+          <t>638159.314292381</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>8.582</t>
+          <t>678034.594325458</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>8.577</t>
+          <t>703814.164186615</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>9.255</t>
+          <t>780552.995271117</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>10.49</t>
+          <t>855942.12098033</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>10.363</t>
+          <t>817562.766851334</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>10.341</t>
+          <t>801179.641228299</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10.264</t>
+          <t>847244.97839317</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>10.899</t>
+          <t>921319.439302112</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11.397</t>
+          <t>954032.554114371</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>11.442</t>
+          <t>994409.912392626</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>410204.355</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>173378.724</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>177658.98</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>200465.652</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>195070.104</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>218529.645</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>226821.661</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>234322.527</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>241245.409</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>254723.212</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>265002.941</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>261603.521</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>213409.31</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>264185.514</t>
-        </is>
-      </c>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>269642.958</t>
-        </is>
-      </c>
-      <c r="R35" t="inlineStr">
-        <is>
-          <t>249743.89</t>
-        </is>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>293085.756</t>
-        </is>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>259023.803</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>268060.815</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>329599.899</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>335953.67</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>372719.335</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>311049.478</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>348559.424</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>348820.698</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>377914.453</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>400236.45</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>133.97</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>101.56</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>101.86</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>83.61</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>92.99</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>76.48</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>74.41</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>72.41</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>71.93</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>66.99</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>63.98</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>68.51</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>111.6</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>79.72</t>
-        </is>
-      </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>77.76</t>
-        </is>
-      </c>
-      <c r="R36" t="inlineStr">
-        <is>
-          <t>95.4</t>
-        </is>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>70.36</t>
-        </is>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>102.75</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>106.32</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>122.78</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>121.49</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>116.44</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>147.96</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>124.06</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>124.75</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>127.06</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>119.43</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>14790220.152</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>204.263</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>174.66</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>175.431</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>174.107</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>157.896</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>148.951</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>143.365</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>154.359</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>149.186</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>5350.221</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>114.147</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>108.178</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>107.948</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>112.564</t>
-        </is>
-      </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>88.942</t>
-        </is>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>94.54</t>
-        </is>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>77.722</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>76.197</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>3656454.949</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>1441197.054</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>1761877.828</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>3569401.952</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>1898075.374</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>1836851.776</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>2004569.992</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>2098539.659</t>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>97828.683623373</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>106405.803467987</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>127472.257808489</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>123033.758114157</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>131756.125689627</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>155170.824144434</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>158615.767897632</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>156881.052768925</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>157820.317748975</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>177020.124774213</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>215887.035550942</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>262276.138322018</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>289199.857153399</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>313011.523644511</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>299253.55414488</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>378196.611973298</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>358632.165059166</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>461524.755000875</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>454443.762694269</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>463815.910675309</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>462748.320149987</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>440309.719263389</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>477020.646754121</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>477617.004116896</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>511124.65304486</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>529404.616372657</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>548741.589742382</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>959758345647.203</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>349467999999.952</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>358615999999.929</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>368084000000.012</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>376466000000.09</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>385658999999.998</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>395592000000.018</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>404006999999.943</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>414776000000.242</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>425362000000.041</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>434550999999.875</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>440838000000.125</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>451574999999.792</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>474799000000.052</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>479308999999.987</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>487993999999.885</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>499304999999.959</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>525179000000.092</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>553049999999.889</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>734280063250.916</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>744089584673.394</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>806729156377.672</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>771291995995.176</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>780974334663.698</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>783977175175.948</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>858089369942.342</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>878220897384.128</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1152128950714.66</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>513668000000.017</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>527164000000.009</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>541781999999.963</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>557220000000.152</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>572673000000.043</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>588924000000.031</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>608937000000.016</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>626418000000.178</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>643870000000.093</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>661152999999.916</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>677546000000.086</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>694188999999.837</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>728739000000.141</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>742967000000.015</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>759095999999.998</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>789674999999.953</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>812305000000.127</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>833343999999.946</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>872184635269.527</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>887118649822.419</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>959002732620.176</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>918913861680.6</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>927625879799.839</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>932634105109.966</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>1023921840443.1</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>1049544495879.78</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>947884351967.033</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>437306286728.229</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>446751527685.21</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>464330265173.903</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>470510591897.853</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>490990108633.345</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>490284296438.545</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>505913221293.333</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>524016073544.629</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>533214889213.811</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>548623227006.306</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>562151381457.801</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>572457237873.269</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>600480205026.043</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>612190087117.027</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>625743350147.808</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>651903073952.974</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>661997375901.575</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>680543535909.779</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>714831401029</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>725600440858.234</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>789857089338.742</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>751294696040.454</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>767262497513.319</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>770176771811.698</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>845519500719.879</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>865021753330.221</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>509605962.530908</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>226434000.000006</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>232371000.000035</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>238824000.000065</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>245646000.00003</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>252472999.999921</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>259664000.000049</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>268625000</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>276499999.99999</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>284299999.999967</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>292032999.999986</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>299340999.99993</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>306806999.99992</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>322316000.000072</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>328614999.999911</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>335847999.99998</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>349548000.00002</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>359597999.999865</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>368902999.99998</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>385540972.611035</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>392785805.810605</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>423835505.57822</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>406318999.080115</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>409760044.778252</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>412145311.10041</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>452678269.077915</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>464148798.826713</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>421049004.851846</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>151570000.000031</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>193136461.841281</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>199224000.000068</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>178220631.084091</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>209803999.99993</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>215542000.00005</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>221794000.000003</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>228109999.999991</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>234321999.999969</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>240182999.99999</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>245129999.999942</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>251234999.999897</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>264129000.000067</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>268166999.999911</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>273667999.999991</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>282859000.000004</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>293757999.999862</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>304271000.000001</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>322021350.749113</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>326708748.308696</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>353592595.641752</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>338212974.756416</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>342195671.459443</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>343657055.006519</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>376265735.332635</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>385211404.766883</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1152128950714.66</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>513668000000.017</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>527164000000.009</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>541781999999.963</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>557220000000.152</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>572673000000.043</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>588924000000.031</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>608937000000.016</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>626418000000.178</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>643870000000.093</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>661152999999.916</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>677546000000.086</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>694188999999.837</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>728739000000.141</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>742967000000.015</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>759095999999.998</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>789674999999.953</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>812305000000.127</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>833343999999.946</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>872184635269.527</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>887118649822.419</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>959002732620.176</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>918913861680.6</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>927625879799.839</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>932634105109.966</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>1023921840443.1</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>1049544495879.78</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>959758345647.203</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>349467999999.952</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>358615999999.929</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>368084000000.012</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>376466000000.09</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>385658999999.998</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>395592000000.018</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>404006999999.943</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>414776000000.242</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>425362000000.041</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>434550999999.875</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>440838000000.125</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>451574999999.792</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>474799000000.052</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>479308999999.987</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>487993999999.885</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>499304999999.959</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>525179000000.092</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>553049999999.889</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>734280063250.916</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>744089584673.394</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>806729156377.672</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>771291995995.176</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>780974334663.698</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>783977175175.948</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>858089369942.342</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>878220897384.128</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>592505.627363977</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>625822.770935417</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>719387.601502714</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>728294.771340205</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>772666.335974688</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>909433.050684548</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>966420.13571787</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>980886.234885506</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>951509.547155193</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>1033662.98439914</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>1220153.80332753</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>1470057.4112649</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>1576461.08679319</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>1814264.24691506</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>1723564.43503782</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>2137998.84945831</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>2275234.94969312</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>2639448.29866594</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>2665874.00674974</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>2833183.26128881</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>2931639.34390094</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>2872245.07720513</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2886518.29150743</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>2971410.24111762</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>3328075.76502697</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>3441069.4918347</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>3556965.5773628</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>227720.213333614</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>256042.832206501</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>286362.097447276</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>297342.43125125</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>317737.228515804</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>379839.83416021</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>403899.871389453</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>414189.644178522</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>399390.301389993</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>432665.376008947</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>515512.900822123</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>606328.362389758</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>646807.888582447</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>757790.947477592</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>714202.581051784</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>843464.697098324</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>952384.313641841</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>1053714.34721384</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>1098639.01092006</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>1156440.16047126</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>1243109.31699867</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>1177781.80006963</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>1187787.16941904</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>1223970.43548487</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>1337978.35153766</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>1385801.7583792</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>1435260.35979208</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
         </is>
       </c>
     </row>
@@ -3609,7 +5855,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3632,36 +5878,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3673,331 +5934,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -4034,6 +6659,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>EXI382</t>
